--- a/Electronic Circuits 1/labs/Projects Gantt Chart.xlsx
+++ b/Electronic Circuits 1/labs/Projects Gantt Chart.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mymailmapuaedu-my.sharepoint.com/personal/gamadrona_mymail_mapua_edu_ph/Documents/My Lectures/Electronic Circuits 1/labs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mymailmapuaedu-my.sharepoint.com/personal/gamadrona_mymail_mapua_edu_ph/Documents/My Lectures/_student notes/Electronic Circuits 1/labs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{227CBE86-D893-4438-A747-56D339908839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA9866F4-8389-4FD8-A39A-EFDB20AEE23D}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="13_ncr:1_{227CBE86-D893-4438-A747-56D339908839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3607FF72-2585-4126-99F3-5DD29010315D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gantt" sheetId="1" r:id="rId1"/>
@@ -526,24 +526,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -599,6 +581,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -630,10 +630,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -899,6 +895,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B1:P24"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="19.5" x14ac:dyDescent="0.5"/>
   <cols>
@@ -909,73 +908,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.5">
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="K1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="L1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="M1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="N1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="O1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="21" t="s">
+      <c r="P1" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="2:16" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="18"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="12"/>
     </row>
     <row r="3" spans="2:16" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="9"/>
@@ -991,10 +990,10 @@
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
-      <c r="P3" s="23"/>
+      <c r="P3" s="17"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.5">
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="18" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="4"/>
@@ -1010,10 +1009,10 @@
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
-      <c r="P4" s="25"/>
+      <c r="P4" s="19"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.5">
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="18" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="5"/>
@@ -1029,10 +1028,10 @@
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
-      <c r="P5" s="25"/>
+      <c r="P5" s="19"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.5">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="18" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="5"/>
@@ -1048,10 +1047,10 @@
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
-      <c r="P6" s="25"/>
+      <c r="P6" s="19"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.5">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="18" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="5"/>
@@ -1067,10 +1066,10 @@
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
-      <c r="P7" s="25"/>
+      <c r="P7" s="19"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.5">
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="18" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="5"/>
@@ -1086,10 +1085,10 @@
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
-      <c r="P8" s="25"/>
+      <c r="P8" s="19"/>
     </row>
     <row r="9" spans="2:16" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="20" t="s">
         <v>28</v>
       </c>
       <c r="C9" s="3"/>
@@ -1105,10 +1104,10 @@
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
-      <c r="P9" s="27"/>
+      <c r="P9" s="21"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.5">
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="18" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="5"/>
@@ -1124,10 +1123,10 @@
       <c r="M10" s="5"/>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
-      <c r="P10" s="25"/>
+      <c r="P10" s="19"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.5">
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="18" t="s">
         <v>26</v>
       </c>
       <c r="C11" s="5"/>
@@ -1143,10 +1142,10 @@
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
       <c r="O11" s="6"/>
-      <c r="P11" s="28"/>
+      <c r="P11" s="22"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.5">
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="18" t="s">
         <v>27</v>
       </c>
       <c r="C12" s="5"/>
@@ -1162,10 +1161,10 @@
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
       <c r="O12" s="6"/>
-      <c r="P12" s="28"/>
+      <c r="P12" s="22"/>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.5">
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C13" s="8"/>
@@ -1181,29 +1180,29 @@
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
       <c r="O13" s="8"/>
-      <c r="P13" s="30"/>
+      <c r="P13" s="24"/>
     </row>
     <row r="14" spans="2:16" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="18"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="12"/>
     </row>
     <row r="15" spans="2:16" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="16" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="9"/>
@@ -1219,10 +1218,10 @@
       <c r="M15" s="9"/>
       <c r="N15" s="9"/>
       <c r="O15" s="9"/>
-      <c r="P15" s="23"/>
+      <c r="P15" s="17"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.5">
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="5"/>
@@ -1238,10 +1237,10 @@
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
-      <c r="P16" s="28"/>
+      <c r="P16" s="22"/>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.5">
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="18" t="s">
         <v>26</v>
       </c>
       <c r="C17" s="5"/>
@@ -1257,10 +1256,10 @@
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
       <c r="O17" s="6"/>
-      <c r="P17" s="28"/>
+      <c r="P17" s="22"/>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.5">
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="18" t="s">
         <v>27</v>
       </c>
       <c r="C18" s="5"/>
@@ -1276,59 +1275,59 @@
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
-      <c r="P18" s="28"/>
+      <c r="P18" s="22"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.5">
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="35"/>
-      <c r="P19" s="36"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="30"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.5">
       <c r="B20" s="2"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.5">
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="15"/>
+      <c r="D21" s="31"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.5">
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.5">
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.5">
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="12"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1341,12 +1340,8 @@
     <mergeCell ref="E24:F24"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.7" bottom="0.7" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="14" scale="63" orientation="landscape" r:id="rId1"/>
-  <headerFooter>
-    <oddFooter>&amp;R&amp;G</oddFooter>
-  </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
+  <printOptions verticalCentered="1"/>
+  <pageMargins left="0" right="0" top="0.25" bottom="0.5" header="0.25" footer="0.25"/>
+  <pageSetup paperSize="14" scale="59" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>